--- a/template_empleados.xlsx
+++ b/template_empleados.xlsx
@@ -1,28 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon60\www\planilla-innova\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0410F3B2-C860-4DD9-8B39-97AA0E22363D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Empleados Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Referencias" sheetId="2" r:id="rId2"/>
-    <sheet name="Instrucciones" sheetId="3" r:id="rId3"/>
+    <sheet name="Empleados Template" sheetId="1" r:id="rId4"/>
+    <sheet name="Referencias" sheetId="2" r:id="rId5"/>
+    <sheet name="Instrucciones" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="176">
   <si>
     <t>CÓDIGO EMPLEADO*</t>
   </si>
@@ -270,88 +265,100 @@
     <t>CARGO</t>
   </si>
   <si>
+    <t>GERENCIA</t>
+  </si>
+  <si>
+    <t>OPERATIVO</t>
+  </si>
+  <si>
+    <t>FUNCIÓN</t>
+  </si>
+  <si>
     <t>CEO</t>
   </si>
   <si>
-    <t>FUNCIÓN</t>
+    <t>GERENTE</t>
+  </si>
+  <si>
+    <t>TECNICO</t>
   </si>
   <si>
     <t>PARTIDA</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10.12.001. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10.12.002. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10.12.005. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10.12.010. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10.12.011. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10.12.012. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.001. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.002. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.003. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.004. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.007. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.008. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.009. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.010. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.012. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.013. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.019. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.020. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.021. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.10.024. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.15.002. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.15.004. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.15.011. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.15.012. - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10.99. - </t>
+    <t>2.10.12.001. - Seguro social por pagar</t>
+  </si>
+  <si>
+    <t>2.10.12.002. - Salarios por pagar</t>
+  </si>
+  <si>
+    <t>2.10.12.005. - Imp. sobre la renta por pagar</t>
+  </si>
+  <si>
+    <t>2.10.12.010. - Seguro educativo por pagar</t>
+  </si>
+  <si>
+    <t>2.10.12.011. - Seguro riesgo profesional por pagar</t>
+  </si>
+  <si>
+    <t>2.10.12.012. - Decimo tercer mes por pagar</t>
+  </si>
+  <si>
+    <t>6.10.10.001. - Sueldos</t>
+  </si>
+  <si>
+    <t>6.10.10.002. - Horas extras</t>
+  </si>
+  <si>
+    <t>6.10.10.003. - Vacaciones</t>
+  </si>
+  <si>
+    <t>6.10.10.004. - Xii mes</t>
+  </si>
+  <si>
+    <t>6.10.10.007. - Gasto de representacion</t>
+  </si>
+  <si>
+    <t>6.10.10.008. - Xiii gasto de representacion</t>
+  </si>
+  <si>
+    <t>6.10.10.009. - Viatico</t>
+  </si>
+  <si>
+    <t>6.10.10.010. - Bonificacion</t>
+  </si>
+  <si>
+    <t>6.10.10.012. - Prima de antiguedad</t>
+  </si>
+  <si>
+    <t>6.10.10.013. - Indemnizacion</t>
+  </si>
+  <si>
+    <t>6.10.10.019. - Seguro social patronal</t>
+  </si>
+  <si>
+    <t>6.10.10.020. - Seguro educativo patronal</t>
+  </si>
+  <si>
+    <t>6.10.10.021. - Seguro riesgo profesional</t>
+  </si>
+  <si>
+    <t>6.10.10.024. - Recargos seguro social</t>
+  </si>
+  <si>
+    <t>6.10.15.002. - Honorarios de contabilidad</t>
+  </si>
+  <si>
+    <t>6.10.15.004. - Honorarios por soporte tecnico</t>
+  </si>
+  <si>
+    <t>6.10.15.011. - Honorarios por desarrollo</t>
+  </si>
+  <si>
+    <t>6.10.15.012. - Honorarios por administracion</t>
+  </si>
+  <si>
+    <t>6.10.99. - IMPUESTO SOBRE LA RENTA</t>
   </si>
   <si>
     <t>ORGANIGRAMA</t>
@@ -462,6 +469,9 @@
     <t xml:space="preserve">   - FOTO: Se asigna automáticamente la imagen por defecto</t>
   </si>
   <si>
+    <t xml:space="preserve">     Ruta: images/facebook-profile-image.jpeg</t>
+  </si>
+  <si>
     <t xml:space="preserve">   - SALARIO POR TIPO DE PLANILLA: Se crea automáticamente un registro de salario</t>
   </si>
   <si>
@@ -535,38 +545,37 @@
   </si>
   <si>
     <t xml:space="preserve">   6. El sistema validará y creará los registros automáticamente</t>
-  </si>
-  <si>
-    <t>GERENTE</t>
-  </si>
-  <si>
-    <t>TECNICO</t>
-  </si>
-  <si>
-    <t>GERENCIA</t>
-  </si>
-  <si>
-    <t>OPERATIVO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -620,25 +629,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -928,35 +929,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:AD3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="22" customWidth="1"/>
-    <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="18" width="17" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="22" customWidth="1"/>
-    <col min="22" max="22" width="26" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
-    <col min="25" max="26" width="20" customWidth="1"/>
-    <col min="27" max="27" width="14" customWidth="1"/>
-    <col min="28" max="28" width="20" customWidth="1"/>
-    <col min="29" max="29" width="18" customWidth="1"/>
-    <col min="30" max="30" width="14" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="true" style="0"/>
+    <col min="2" max="2" width="20" customWidth="true" style="0"/>
+    <col min="3" max="3" width="20" customWidth="true" style="0"/>
+    <col min="4" max="4" width="25" customWidth="true" style="0"/>
+    <col min="5" max="5" width="30" customWidth="true" style="0"/>
+    <col min="6" max="6" width="18" customWidth="true" style="0"/>
+    <col min="7" max="7" width="18" customWidth="true" style="0"/>
+    <col min="8" max="8" width="15" customWidth="true" style="0"/>
+    <col min="9" max="9" width="12" customWidth="true" style="0"/>
+    <col min="10" max="10" width="18" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18" customWidth="true" style="0"/>
+    <col min="12" max="12" width="18" customWidth="true" style="0"/>
+    <col min="13" max="13" width="18" customWidth="true" style="0"/>
+    <col min="14" max="14" width="18" customWidth="true" style="0"/>
+    <col min="15" max="15" width="22" customWidth="true" style="0"/>
+    <col min="16" max="16" width="15" customWidth="true" style="0"/>
+    <col min="17" max="17" width="17" customWidth="true" style="0"/>
+    <col min="18" max="18" width="17" customWidth="true" style="0"/>
+    <col min="19" max="19" width="18" customWidth="true" style="0"/>
+    <col min="20" max="20" width="16" customWidth="true" style="0"/>
+    <col min="21" max="21" width="22" customWidth="true" style="0"/>
+    <col min="22" max="22" width="26" customWidth="true" style="0"/>
+    <col min="23" max="23" width="16" customWidth="true" style="0"/>
+    <col min="24" max="24" width="18" customWidth="true" style="0"/>
+    <col min="25" max="25" width="20" customWidth="true" style="0"/>
+    <col min="26" max="26" width="20" customWidth="true" style="0"/>
+    <col min="27" max="27" width="14" customWidth="true" style="0"/>
+    <col min="28" max="28" width="20" customWidth="true" style="0"/>
+    <col min="29" max="29" width="18" customWidth="true" style="0"/>
+    <col min="30" max="30" width="14" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1048,7 +1060,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1104,10 +1116,10 @@
         <v>1</v>
       </c>
       <c r="S2">
-        <v>1500</v>
+        <v>1500.0</v>
       </c>
       <c r="T2">
-        <v>200</v>
+        <v>200.0</v>
       </c>
       <c r="U2">
         <v>1</v>
@@ -1124,6 +1136,7 @@
       <c r="Y2" t="s">
         <v>36</v>
       </c>
+      <c r="Z2"/>
       <c r="AA2" t="s">
         <v>43</v>
       </c>
@@ -1137,7 +1150,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -1193,10 +1206,10 @@
         <v>2</v>
       </c>
       <c r="S3">
-        <v>1200</v>
+        <v>1200.0</v>
       </c>
       <c r="T3">
-        <v>150</v>
+        <v>150.0</v>
       </c>
       <c r="U3">
         <v>1</v>
@@ -1230,21 +1243,35 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="true" style="0"/>
+    <col min="2" max="2" width="10" customWidth="true" style="0"/>
+    <col min="3" max="3" width="50" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>63</v>
       </c>
@@ -1255,7 +1282,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1266,7 +1293,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -1277,18 +1304,18 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>68</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -1299,7 +1326,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -1310,7 +1337,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -1321,7 +1348,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -1332,7 +1359,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>71</v>
       </c>
@@ -1343,7 +1370,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -1354,7 +1381,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -1365,7 +1392,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>79</v>
       </c>
@@ -1376,7 +1403,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>81</v>
       </c>
@@ -1384,10 +1411,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -1395,643 +1422,700 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B18">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B19">
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B20">
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B21">
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B22">
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B23">
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B28">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B29">
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B30">
         <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B31">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B32">
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B33">
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B34">
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B35">
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B36">
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B37">
         <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B38">
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B39">
         <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B40">
         <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B41">
         <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B42">
         <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:A68"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="80" customWidth="1"/>
+    <col min="1" max="1" width="80" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2"/>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14"/>
+    </row>
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23"/>
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27"/>
+    </row>
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35"/>
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37"/>
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46"/>
+    </row>
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52"/>
+    </row>
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61"/>
+    </row>
+    <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>170</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>